--- a/1_Data/Lee_2026_BritJPsy/Exp2/Codebook_Lee_2026_BritJPsy_Exp2_Clean.xlsx
+++ b/1_Data/Lee_2026_BritJPsy/Exp2/Codebook_Lee_2026_BritJPsy_Exp2_Clean.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">Variable_name</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t xml:space="preserve">1 (correct); 0 (incorrect, key pressed within deadline but wrong); NA (no response / timeout; authors counted timeouts as incorrect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task type: shape-matching = shape-label matching without a self-referential identity task (here: shape-emotion face associations; the self/stranger name prime is extraIV1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shape-matching</t>
   </si>
 </sst>
 </file>
@@ -475,10 +481,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
